--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="107">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Rang de la vaccination</t>
+    <t>Entrée Rang de la vaccination</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -340,6 +340,9 @@
   <si>
     <t xml:space="preserve">integer
 </t>
+  </si>
+  <si>
+    <t>Rang de la vaccination</t>
   </si>
 </sst>
 </file>
@@ -1822,10 +1825,10 @@
         <v>105</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-dose-number.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
